--- a/outputs/13-1.xlsx
+++ b/outputs/13-1.xlsx
@@ -313,60 +313,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -622,869 +626,869 @@
   <dimension ref="A1:F55"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="6" t="n">
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F3" s="7"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>230</v>
       </c>
-      <c r="F5" s="7"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>45325</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="6" t="n">
+      <c r="D7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="F8" s="7"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="6" t="n">
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="5" t="n">
+      <c r="A10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6" t="n">
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="6" t="n">
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="6" t="n">
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>140</v>
       </c>
-      <c r="F12" s="7"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5" t="n">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="6" t="n">
+      <c r="D13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F13" s="7"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1"/>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="6" t="n">
+      <c r="D18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F18" s="7"/>
+      <c r="F18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="6" t="n">
+      <c r="D19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="7" t="n">
         <v>320</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="6" t="n">
+      <c r="D20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>330</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="6" t="n">
+      <c r="D21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="7" t="n">
         <v>320</v>
       </c>
-      <c r="F21" s="7"/>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="6" t="n">
+      <c r="D22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="7" t="n">
         <v>1225</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="6" t="n">
+      <c r="D23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F23" s="7"/>
+      <c r="F23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="6" t="n">
+      <c r="D24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="F24" s="7"/>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B25" s="5" t="n">
+      <c r="A25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="6" t="n">
+      <c r="D25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="7" t="n">
         <v>330</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="6" t="n">
+      <c r="D26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="7" t="n">
         <v>125</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="F27" s="7"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B28" s="5" t="n">
+      <c r="A28" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>144</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="6" t="n">
+      <c r="D29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="7" t="n">
         <v>560</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="D30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="7" t="n">
         <v>125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="6" t="n">
+      <c r="D31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="7" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="6" t="n">
+      <c r="D32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="7" t="n">
         <v>126</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="10"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="1"/>
-      <c r="C35" s="2" t="s">
+      <c r="B35" s="2"/>
+      <c r="C35" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="6" t="n">
+      <c r="D37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="F37" s="7"/>
+      <c r="F37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="6" t="n">
+      <c r="D38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="7" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="6" t="n">
+      <c r="D39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="7" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="6" t="n">
+      <c r="D40" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F40" s="7"/>
+      <c r="F40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="6" t="n">
+      <c r="D41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="7" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="6" t="n">
+      <c r="D42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="7" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="6" t="n">
+      <c r="D43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="7" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B44" s="5" t="n">
+      <c r="A44" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="6" t="n">
+      <c r="D44" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="7" t="n">
         <v>230</v>
       </c>
-      <c r="F44" s="7"/>
+      <c r="F44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>560</v>
       </c>
-      <c r="F45" s="7"/>
+      <c r="F45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B47" s="5" t="n">
+      <c r="A47" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B47" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="6" t="n">
+      <c r="D48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="7" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="6" t="n">
+      <c r="D49" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="F49" s="7"/>
+      <c r="F49" s="8"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="6" t="n">
+      <c r="D50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="F50" s="7"/>
+      <c r="F50" s="8"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="6" t="n">
+      <c r="D51" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="7" t="n">
         <v>126</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="6" t="n">
+      <c r="D52" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="F52" s="7"/>
+      <c r="F52" s="8"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="6" t="n">
+      <c r="D53" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="7" t="n">
         <v>138</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="6" t="n">
+      <c r="D54" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="7" t="n">
         <v>144</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="6" t="n">
+      <c r="D55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="7" t="n">
         <v>150</v>
       </c>
     </row>
@@ -1507,390 +1511,390 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>45325</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="6" t="n">
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="F3" s="11"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>45344</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="n">
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>420</v>
       </c>
-      <c r="F4" s="11"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>45344</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="7" t="n">
         <v>340</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>225</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>470</v>
       </c>
-      <c r="F7" s="11"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>140</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="6" t="n">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="7" t="n">
         <f aca="false">SUM(D3:D9)</f>
         <v>1860</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>45344</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="6" t="n">
+      <c r="C15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="7" t="n">
         <v>1545</v>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>45344</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="6" t="n">
+      <c r="C16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="F16" s="11"/>
+      <c r="F16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="6" t="n">
+      <c r="C17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>771</v>
       </c>
-      <c r="F17" s="11"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <v>274</v>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>45354</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="6" t="n">
+      <c r="C19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="7" t="n">
         <v>1215</v>
       </c>
-      <c r="F19" s="11"/>
+      <c r="F19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="6" t="n">
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="7" t="n">
         <f aca="false">SUM(D15:D19)</f>
         <v>4755</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>45346</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="6" t="n">
+      <c r="C25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="7" t="n">
         <v>1990</v>
       </c>
-      <c r="F25" s="11"/>
+      <c r="F25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>45346</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="6" t="n">
+      <c r="C26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="7" t="n">
         <v>1350</v>
       </c>
-      <c r="F26" s="11"/>
+      <c r="F26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="6" t="n">
+      <c r="C27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="7" t="n">
         <v>230</v>
       </c>
-      <c r="F27" s="11"/>
+      <c r="F27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="7" t="n">
         <v>1490</v>
       </c>
-      <c r="F28" s="11"/>
+      <c r="F28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>45385</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="6" t="n">
+      <c r="C29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="F29" s="11"/>
+      <c r="F29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="6" t="n">
+      <c r="C30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="7" t="n">
         <v>534</v>
       </c>
-      <c r="F30" s="11"/>
+      <c r="F30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>45415</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="6" t="n">
+      <c r="C31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="7" t="n">
         <v>401</v>
       </c>
-      <c r="F31" s="11"/>
+      <c r="F31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="6" t="n">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="7" t="n">
         <f aca="false">SUM(D25:D31)</f>
         <v>6495</v>
       </c>
-      <c r="F32" s="11"/>
+      <c r="F32" s="12"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
